--- a/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,35 +471,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Security; Scalability; Availability and reliability</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Service-oriented</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -509,59 +509,153 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored to be able to process them in the analytical module.</t>
+          <t>Dona la capacitat de manegar caigudes parcials del sistema, manegant quins serveis estan en funcionament en tot moment.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.635</v>
+        <v>0.7309</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
+          <t>CF_M01_AD05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gives the ability to handle partial system crashes</t>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M01_C08</t>
+          <t>*CF_M01_C11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>API Gateway Service</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The only component that interacts directly with the presentation layer is the Api Gateway module. This is because the Api Gateway microservices design pattern is followed. This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: It increases the security of the system by reducing the gateways to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.5718</v>
+        <v>0.5597</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6721</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Speed and latency</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AWS cloud services set</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6481</v>
       </c>
     </row>
   </sheetData>
